--- a/data/trans_orig/P1434-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1434-Provincia-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259246</t>
+          <t>259582</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269557</t>
+          <t>269492</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259246</t>
+          <t>259582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269557</t>
+          <t>269492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>24421</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>24421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>469090</t>
+          <t>468654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>484810</t>
+          <t>485002</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469090</t>
+          <t>468654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484810</t>
+          <t>485002</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15052</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15052</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303794</t>
+          <t>304932</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315003</t>
+          <t>315768</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>303794</t>
+          <t>304932</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315003</t>
+          <t>315768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>11756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>11756</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347128</t>
+          <t>346915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356908</t>
+          <t>356892</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347128</t>
+          <t>346915</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>356908</t>
+          <t>356892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>823</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195120</t>
+          <t>194245</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202498</t>
+          <t>202485</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>195120</t>
+          <t>194245</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202498</t>
+          <t>202485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261120</t>
+          <t>260891</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269845</t>
+          <t>269847</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261120</t>
+          <t>260891</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269845</t>
+          <t>269847</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33202</t>
+          <t>29591</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33202</t>
+          <t>29591</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>581825</t>
+          <t>585436</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>601722</t>
+          <t>602633</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>581825</t>
+          <t>585436</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>601722</t>
+          <t>602633</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33145</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58178</t>
+          <t>58848</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33145</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58178</t>
+          <t>58848</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>685617</t>
+          <t>684947</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>710650</t>
+          <t>711398</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>685617</t>
+          <t>684947</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>710650</t>
+          <t>711398</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -2577,12 +2577,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>86266</t>
+          <t>88774</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>127218</t>
+          <t>126899</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>86266</t>
+          <t>88774</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>127218</t>
+          <t>126899</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3149325</t>
+          <t>3149644</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3190277</t>
+          <t>3187769</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3149325</t>
+          <t>3149644</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3190277</t>
+          <t>3187769</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>10678</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27830</t>
+          <t>29113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>10678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27830</t>
+          <t>29113</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>266908</t>
+          <t>265625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284678</t>
+          <t>284060</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266908</t>
+          <t>265625</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284678</t>
+          <t>284060</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>29120</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>29120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>475889</t>
+          <t>476407</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495183</t>
+          <t>495274</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475889</t>
+          <t>476407</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495183</t>
+          <t>495274</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>12922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>12922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309829</t>
+          <t>311124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321951</t>
+          <t>321972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>309829</t>
+          <t>311124</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321951</t>
+          <t>321972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18727</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18727</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>355255</t>
+          <t>355761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369682</t>
+          <t>370399</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>355255</t>
+          <t>355761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369682</t>
+          <t>370399</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198995</t>
+          <t>199861</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210416</t>
+          <t>210426</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198995</t>
+          <t>199861</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>210416</t>
+          <t>210426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261302</t>
+          <t>261313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271878</t>
+          <t>271821</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261302</t>
+          <t>261313</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271878</t>
+          <t>271821</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16514</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38023</t>
+          <t>38086</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16514</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38023</t>
+          <t>38086</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>622574</t>
+          <t>622511</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>644083</t>
+          <t>643074</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>622574</t>
+          <t>622511</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>644083</t>
+          <t>643074</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4656,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25288</t>
+          <t>24244</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49201</t>
+          <t>50312</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25288</t>
+          <t>24244</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49201</t>
+          <t>50312</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4734,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>729897</t>
+          <t>728786</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>753810</t>
+          <t>754854</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>729897</t>
+          <t>728786</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>753810</t>
+          <t>754854</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -4894,12 +4894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>102054</t>
+          <t>101960</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>149623</t>
+          <t>147982</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -4929,12 +4929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>102054</t>
+          <t>101960</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>149623</t>
+          <t>147982</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3274964</t>
+          <t>3276605</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3322533</t>
+          <t>3322627</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3274964</t>
+          <t>3276605</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3322533</t>
+          <t>3322627</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -5307,12 +5307,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26714</t>
+          <t>26137</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26714</t>
+          <t>26137</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267047</t>
+          <t>267624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282720</t>
+          <t>283293</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267047</t>
+          <t>267624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282720</t>
+          <t>283293</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483385</t>
+          <t>484069</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>497114</t>
+          <t>497640</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>483385</t>
+          <t>484069</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497114</t>
+          <t>497640</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -5783,12 +5783,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25170</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25170</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -5861,12 +5861,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293395</t>
+          <t>293493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309522</t>
+          <t>308461</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5876,12 +5876,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>293395</t>
+          <t>293493</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>309522</t>
+          <t>308461</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6071,12 +6071,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347947</t>
+          <t>348276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362888</t>
+          <t>362546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347947</t>
+          <t>348276</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362888</t>
+          <t>362546</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200324</t>
+          <t>200055</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209390</t>
+          <t>209305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200324</t>
+          <t>200055</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>209390</t>
+          <t>209305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -6497,12 +6497,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -6575,12 +6575,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251617</t>
+          <t>251881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261007</t>
+          <t>260766</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251617</t>
+          <t>251881</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261007</t>
+          <t>260766</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6625,12 +6625,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31015</t>
+          <t>30150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12530</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31015</t>
+          <t>30150</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>625543</t>
+          <t>626408</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>644028</t>
+          <t>644130</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>625543</t>
+          <t>626408</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>644028</t>
+          <t>644130</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -6973,12 +6973,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31887</t>
+          <t>32807</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31887</t>
+          <t>32807</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>746696</t>
+          <t>745776</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>763775</t>
+          <t>764161</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7086,12 +7086,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>746696</t>
+          <t>745776</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>763775</t>
+          <t>764161</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -7211,12 +7211,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92176</t>
+          <t>91109</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>133426</t>
+          <t>131154</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>92176</t>
+          <t>91109</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>133426</t>
+          <t>131154</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3260924</t>
+          <t>3263196</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3302174</t>
+          <t>3303241</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7324,12 +7324,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3260924</t>
+          <t>3263196</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3302174</t>
+          <t>3303241</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -7619,32 +7619,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7654,32 +7654,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -7697,32 +7697,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>299572</t>
+          <t>307444</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>293317</t>
+          <t>300434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304863</t>
+          <t>312160</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,32 +7732,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>299572</t>
+          <t>307444</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293317</t>
+          <t>300434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304863</t>
+          <t>312160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -7775,17 +7775,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7810,17 +7810,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7857,32 +7857,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7892,32 +7892,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -7935,32 +7935,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>503991</t>
+          <t>515829</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496498</t>
+          <t>507010</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>509385</t>
+          <t>521354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7970,32 +7970,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>503991</t>
+          <t>515829</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>496498</t>
+          <t>507010</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509385</t>
+          <t>521354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -8013,17 +8013,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514816</t>
+          <t>527125</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514816</t>
+          <t>527125</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514816</t>
+          <t>527125</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8048,17 +8048,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514816</t>
+          <t>527125</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514816</t>
+          <t>527125</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514816</t>
+          <t>527125</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8095,32 +8095,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>23805</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32555</t>
+          <t>32087</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8130,32 +8130,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>23805</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32555</t>
+          <t>32087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -8173,32 +8173,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>290111</t>
+          <t>290567</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281827</t>
+          <t>282285</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297197</t>
+          <t>297351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8208,32 +8208,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>290111</t>
+          <t>290567</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>281827</t>
+          <t>282285</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>297197</t>
+          <t>297351</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -8251,17 +8251,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314382</t>
+          <t>314372</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314382</t>
+          <t>314372</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314382</t>
+          <t>314372</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8286,17 +8286,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>314382</t>
+          <t>314372</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>314382</t>
+          <t>314372</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>314382</t>
+          <t>314372</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8333,32 +8333,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>22098</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29624</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8368,32 +8368,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>22098</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29624</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -8411,32 +8411,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>288416</t>
+          <t>346226</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>277821</t>
+          <t>336332</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295064</t>
+          <t>354122</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8446,32 +8446,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>288416</t>
+          <t>346226</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>277821</t>
+          <t>336332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>295064</t>
+          <t>354122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -8489,17 +8489,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>307445</t>
+          <t>368324</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>307445</t>
+          <t>368324</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>307445</t>
+          <t>368324</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>307445</t>
+          <t>368324</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>307445</t>
+          <t>368324</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>307445</t>
+          <t>368324</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8571,32 +8571,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8606,32 +8606,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -8649,32 +8649,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>168671</t>
+          <t>195220</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164001</t>
+          <t>189972</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>172271</t>
+          <t>198630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8684,32 +8684,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>168671</t>
+          <t>195220</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>164001</t>
+          <t>189972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>172271</t>
+          <t>198630</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -8727,17 +8727,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>177506</t>
+          <t>204363</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>177506</t>
+          <t>204363</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>177506</t>
+          <t>204363</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8762,17 +8762,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>177506</t>
+          <t>204363</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>177506</t>
+          <t>204363</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>177506</t>
+          <t>204363</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8809,32 +8809,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25183</t>
+          <t>25108</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33277</t>
+          <t>32890</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8844,32 +8844,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25183</t>
+          <t>25108</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33277</t>
+          <t>32890</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -8887,32 +8887,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>244453</t>
+          <t>245599</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236359</t>
+          <t>237817</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250345</t>
+          <t>251856</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8922,32 +8922,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>244453</t>
+          <t>245599</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236359</t>
+          <t>237817</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250345</t>
+          <t>251856</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -8965,17 +8965,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9000,17 +9000,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9047,32 +9047,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>28459</t>
+          <t>32596</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20363</t>
+          <t>24246</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>45781</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9082,32 +9082,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>28459</t>
+          <t>32596</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20363</t>
+          <t>24246</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>45781</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -9125,32 +9125,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>590238</t>
+          <t>680814</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>580416</t>
+          <t>667629</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598334</t>
+          <t>689164</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9160,32 +9160,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>590238</t>
+          <t>680814</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>580416</t>
+          <t>667629</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>598334</t>
+          <t>689164</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -9203,17 +9203,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>618697</t>
+          <t>713410</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>618697</t>
+          <t>713410</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>618697</t>
+          <t>713410</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9238,17 +9238,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>618697</t>
+          <t>713410</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>618697</t>
+          <t>713410</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>618697</t>
+          <t>713410</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9285,32 +9285,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>51764</t>
+          <t>57630</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>45683</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>75996</t>
+          <t>72750</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9320,32 +9320,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>51764</t>
+          <t>57630</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>45683</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75996</t>
+          <t>72750</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -9363,32 +9363,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>874322</t>
+          <t>737483</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>850090</t>
+          <t>722363</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>903933</t>
+          <t>749430</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9398,32 +9398,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>874322</t>
+          <t>737483</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>850090</t>
+          <t>722363</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>903933</t>
+          <t>749430</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -9441,17 +9441,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>926086</t>
+          <t>795113</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>926086</t>
+          <t>795113</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>926086</t>
+          <t>795113</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9476,17 +9476,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>926086</t>
+          <t>795113</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>926086</t>
+          <t>795113</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>926086</t>
+          <t>795113</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>180237</t>
+          <t>193076</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>139447</t>
+          <t>170780</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>204671</t>
+          <t>217408</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>180237</t>
+          <t>193076</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>139447</t>
+          <t>170780</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>204671</t>
+          <t>217408</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3259774</t>
+          <t>3319184</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3235340</t>
+          <t>3294852</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3300564</t>
+          <t>3341480</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3259774</t>
+          <t>3319184</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3235340</t>
+          <t>3294852</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3300564</t>
+          <t>3341480</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -9679,17 +9679,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9714,17 +9714,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
